--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,10 +418,10 @@
         <v>TAY1381</v>
       </c>
       <c r="B2" t="str">
-        <v>030217141005</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>55000</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>individual</v>
@@ -432,10 +432,10 @@
         <v>NCG9826</v>
       </c>
       <c r="B3" t="str">
-        <v>030217141005</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>55000</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v>individual</v>
@@ -446,130 +446,18 @@
         <v>VL3046</v>
       </c>
       <c r="B4" t="str">
-        <v>030217141005</v>
+        <v/>
       </c>
       <c r="C4" t="str">
-        <v>55000</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>PHS2981</v>
-      </c>
-      <c r="B5" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C5" t="str">
-        <v>55000</v>
-      </c>
-      <c r="D5" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>WYN3837</v>
-      </c>
-      <c r="B6" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C6" t="str">
-        <v>55000</v>
-      </c>
-      <c r="D6" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>VBY7199</v>
-      </c>
-      <c r="B7" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C7" t="str">
-        <v>55000</v>
-      </c>
-      <c r="D7" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>NDD6099</v>
-      </c>
-      <c r="B8" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C8" t="str">
-        <v>55000</v>
-      </c>
-      <c r="D8" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>CDR7577</v>
-      </c>
-      <c r="B9" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C9" t="str">
-        <v>55000</v>
-      </c>
-      <c r="D9" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ALM8454</v>
-      </c>
-      <c r="B10" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C10" t="str">
-        <v>55000</v>
-      </c>
-      <c r="D10" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>VFH174</v>
-      </c>
-      <c r="B11" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C11" t="str">
-        <v>55000</v>
-      </c>
-      <c r="D11" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>RS6686</v>
-      </c>
-      <c r="B12" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C12" t="str">
-        <v>55000</v>
-      </c>
-      <c r="D12" t="str">
         <v>individual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,49 +415,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TAY1381</v>
+        <v>PHS2981</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>030217141005</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>55000</v>
       </c>
       <c r="D2" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>NCG9826</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>VL3046</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
         <v>individual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,18 +418,144 @@
         <v>PHS2981</v>
       </c>
       <c r="B2" t="str">
-        <v>030217141005</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>55000</v>
+        <v/>
       </c>
       <c r="D2" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>WYN3837</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>VBY7199</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>NDD6099</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CDR7577</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ALM8454</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>VFH174</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>RS6686</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>JQP2685</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>BNR9936</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
         <v>individual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PHS2981</v>
+        <v>VFH174</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>WYN3837</v>
+        <v>RS6686</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -443,7 +443,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>VBY7199</v>
+        <v>JQP2685</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -452,110 +452,12 @@
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>NDD6099</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>CDR7577</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ALM8454</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>VFH174</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>RS6686</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>JQP2685</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>BNR9936</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
         <v>individual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VFH174</v>
+        <v>JQP2685</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>RS6686</v>
+        <v>BNR9936</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -443,7 +443,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>JQP2685</v>
+        <v>BPM4990</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -452,12 +452,26 @@
         <v/>
       </c>
       <c r="D4" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>PMJ2431</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
         <v>individual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>JQP2685</v>
+        <v>TDB9139</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>BNR9936</v>
+        <v>VCA5484</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -443,7 +443,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>BPM4990</v>
+        <v>PLD1301</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -457,21 +457,259 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>CCV939</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TAY1381</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>NCG9826</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>VL3046</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>PHS2981</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>WYN3837</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>VBY7199</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>NDD6099</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CDR7577</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>ALM8454</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>VFH174</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>RS6686</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>JQP2685</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>BNR9936</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>BPM4990</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>PMJ2431</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>AHA430</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>VNJ857</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
         <v>individual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TDB9139</v>
+        <v>JQP2685</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>VCA5484</v>
+        <v>BNR9936</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -443,7 +443,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PLD1301</v>
+        <v>BPM4990</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -457,7 +457,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CCV939</v>
+        <v>PMJ2431</v>
       </c>
       <c r="B5" t="str">
         <v/>
@@ -471,7 +471,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TAY1381</v>
+        <v>AHA430</v>
       </c>
       <c r="B6" t="str">
         <v/>
@@ -485,7 +485,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>NCG9826</v>
+        <v>VNJ857</v>
       </c>
       <c r="B7" t="str">
         <v/>
@@ -497,219 +497,9 @@
         <v>individual</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>VL3046</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>PHS2981</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>WYN3837</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>VBY7199</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>NDD6099</v>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>CDR7577</v>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>ALM8454</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>VFH174</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>RS6686</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>JQP2685</v>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>BNR9936</v>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>BPM4990</v>
-      </c>
-      <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>PMJ2431</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>AHA430</v>
-      </c>
-      <c r="B21" t="str">
-        <v/>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>VNJ857</v>
-      </c>
-      <c r="B22" t="str">
-        <v/>
-      </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <v>individual</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>JQP2685</v>
+        <v>NDD6099</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -424,82 +424,12 @@
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>BNR9936</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>BPM4990</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>PMJ2431</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>AHA430</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>VNJ857</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
         <v>individual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>NDD6099</v>
+        <v>MCW3799</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -424,12 +424,54 @@
         <v/>
       </c>
       <c r="D2" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>MCA2388</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>BQT3130</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>NDC7743</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
         <v>individual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -469,9 +469,23 @@
         <v>individual</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>EABTJB7</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>individual</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>MCW3799</v>
+        <v>JQA2210</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MCA2388</v>
+        <v>PMH4872</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -438,54 +438,12 @@
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>BQT3130</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>NDC7743</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>EABTJB7</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
         <v>individual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>JQA2210</v>
+        <v>VAJ124</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>PMH4872</v>
+        <v>VAH0124</v>
       </c>
       <c r="B3" t="str">
         <v/>

--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VAJ124</v>
+        <v>VMV4697</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -424,12 +424,12 @@
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>individual</v>
+        <v>company</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>VAH0124</v>
+        <v>BKD381</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -438,12 +438,586 @@
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>individual</v>
+        <v>company</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>QS9490E</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FF9931</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>WPG31</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AKF5409</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>JXQ6278</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>VAY12</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>JUM89</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SM5017</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SM5017</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CEG9211</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>QBH1286</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>MALAYSIA3187</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>WA883Y</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>BCF1079</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>VMX6457</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>VGV6192</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>VCN1552</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>VAY1881</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>VPB4370</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>BRW3175</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>AEU6895</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>PRL3429</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>JWC4641</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>QTN4046</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>WXT3300</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>JWA9658</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>KDW3</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>WXM86</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>KX8</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>QCF9853</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>BNK7069</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>KAC24</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>WUH8456</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>WUG76</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>UITM2093</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>JXU6420</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>JXN8717</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>WDX2897</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>WDX2897</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>PNP2</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>KFP7077</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v>company</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,10 +415,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>JXB2061</v>
+        <v>BHA2468</v>
       </c>
       <c r="B2" t="str">
-        <v>201901043732</v>
+        <v>030303-A</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -429,10 +429,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>VNU9093</v>
+        <v>CCF5361</v>
       </c>
       <c r="B3" t="str">
-        <v>201301027897</v>
+        <v>030303-A</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -443,10 +443,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>VHS5036</v>
+        <v>QAB3377M</v>
       </c>
       <c r="B4" t="str">
-        <v>201401035570</v>
+        <v>030303-A</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -457,10 +457,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SYX4879</v>
+        <v>VDA9008</v>
       </c>
       <c r="B5" t="str">
-        <v>749928P</v>
+        <v>030303-A</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -471,21 +471,49 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SYX4841</v>
+        <v>WYX8315</v>
       </c>
       <c r="B6" t="str">
-        <v>749928P</v>
+        <v>030303-A</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>WVY6520</v>
+      </c>
+      <c r="B7" t="str">
+        <v>030303-A</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>WVY6520</v>
+      </c>
+      <c r="B8" t="str">
+        <v>030303-A</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
         <v>company</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,10 +415,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BHA2468</v>
+        <v>WKR590</v>
       </c>
       <c r="B2" t="str">
-        <v>030303-A</v>
+        <v>030217141005</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -429,10 +429,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CCF5361</v>
+        <v>MU1977</v>
       </c>
       <c r="B3" t="str">
-        <v>030303-A</v>
+        <v>030217141005</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -443,10 +443,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>QAB3377M</v>
+        <v>QAA8160F</v>
       </c>
       <c r="B4" t="str">
-        <v>030303-A</v>
+        <v>030217141005</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -457,63 +457,21 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>VDA9008</v>
+        <v>WWK7705</v>
       </c>
       <c r="B5" t="str">
-        <v>030303-A</v>
+        <v>030217141005</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
-        <v>company</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>WYX8315</v>
-      </c>
-      <c r="B6" t="str">
-        <v>030303-A</v>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v>company</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>WVY6520</v>
-      </c>
-      <c r="B7" t="str">
-        <v>030303-A</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>company</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>WVY6520</v>
-      </c>
-      <c r="B8" t="str">
-        <v>030303-A</v>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
         <v>company</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,10 +415,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>WKR590</v>
+        <v>PFE2883</v>
       </c>
       <c r="B2" t="str">
-        <v>030217141005</v>
+        <v>030301-A</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -429,10 +429,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MU1977</v>
+        <v>WWX2121</v>
       </c>
       <c r="B3" t="str">
-        <v>030217141005</v>
+        <v>030301-A</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -443,10 +443,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>QAA8160F</v>
+        <v>VPA2184</v>
       </c>
       <c r="B4" t="str">
-        <v>030217141005</v>
+        <v>030301-A</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -457,21 +457,511 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>WWK7705</v>
+        <v>WXB8616</v>
       </c>
       <c r="B5" t="str">
-        <v>030217141005</v>
+        <v>030301-A</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>JPF8760</v>
+      </c>
+      <c r="B6" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>WYY2299</v>
+      </c>
+      <c r="B7" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>NDM5588</v>
+      </c>
+      <c r="B8" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ST830H</v>
+      </c>
+      <c r="B9" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SMP7</v>
+      </c>
+      <c r="B10" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>WC9739N</v>
+      </c>
+      <c r="B11" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AHG385</v>
+      </c>
+      <c r="B12" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>QAL7209</v>
+      </c>
+      <c r="B13" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>WND7312</v>
+      </c>
+      <c r="B14" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>WJC2562</v>
+      </c>
+      <c r="B15" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>WGS4974</v>
+      </c>
+      <c r="B16" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>BHR6643</v>
+      </c>
+      <c r="B17" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>BPE2868</v>
+      </c>
+      <c r="B18" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>VLB8603</v>
+      </c>
+      <c r="B19" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>JNP5869</v>
+      </c>
+      <c r="B20" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SB9979F</v>
+      </c>
+      <c r="B21" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>VBW1332</v>
+      </c>
+      <c r="B22" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>WQQ8293</v>
+      </c>
+      <c r="B23" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SU7399N</v>
+      </c>
+      <c r="B24" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>PGU1558</v>
+      </c>
+      <c r="B25" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>WWD1881</v>
+      </c>
+      <c r="B26" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>PNC2325</v>
+      </c>
+      <c r="B27" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SMB9936</v>
+      </c>
+      <c r="B28" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>AHB7975</v>
+      </c>
+      <c r="B29" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>VFT1939</v>
+      </c>
+      <c r="B30" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>VFT1939</v>
+      </c>
+      <c r="B31" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>VPC3997</v>
+      </c>
+      <c r="B32" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>VPC3997</v>
+      </c>
+      <c r="B33" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>QS1436Q</v>
+      </c>
+      <c r="B34" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>PKF5320</v>
+      </c>
+      <c r="B35" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>VCB7023</v>
+      </c>
+      <c r="B36" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>QSQ5120</v>
+      </c>
+      <c r="B37" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>WNX3548</v>
+      </c>
+      <c r="B38" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>VLN738</v>
+      </c>
+      <c r="B39" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v>company</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>SAA44B</v>
+      </c>
+      <c r="B40" t="str">
+        <v>030301-A</v>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
         <v>company</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D40"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -1,44 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet sheetId="1" name="Vehicles" state="visible" r:id="rId4"/>
+    <sheet name="Vehicles" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Vehicle Number</t>
-  </si>
-  <si>
-    <t>IC Number</t>
-  </si>
-  <si>
-    <t>Postcode</t>
-  </si>
-  <si>
-    <t>Vehicle Category</t>
-  </si>
-  <si>
-    <t>JKC9998</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -62,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -401,31 +396,292 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D20"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Vehicle Number</v>
+      </c>
+      <c r="B1" t="str">
+        <v>IC Number</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Postcode</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Vehicle Category</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>JVK1779</v>
+      </c>
+      <c r="B2" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PRR5421</v>
+      </c>
+      <c r="B3" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>WB7932R</v>
+      </c>
+      <c r="B4" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>WTX9642</v>
+      </c>
+      <c r="B5" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>WEN7866</v>
+      </c>
+      <c r="B6" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>MCH2151</v>
+      </c>
+      <c r="B7" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>WTX9642</v>
+      </c>
+      <c r="B8" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>VMM949</v>
+      </c>
+      <c r="B9" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>JSS9468</v>
+      </c>
+      <c r="B10" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>RW3512</v>
+      </c>
+      <c r="B11" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>BKN9186</v>
+      </c>
+      <c r="B12" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>JLY4743</v>
+      </c>
+      <c r="B13" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>VBY8385</v>
+      </c>
+      <c r="B14" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>JPK5366</v>
+      </c>
+      <c r="B15" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>JGC7679</v>
+      </c>
+      <c r="B16" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>JLY4743</v>
+      </c>
+      <c r="B17" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>VPF1134</v>
+      </c>
+      <c r="B18" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>VCK772</v>
+      </c>
+      <c r="B19" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>individual</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>VDS5747</v>
+      </c>
+      <c r="B20" t="str">
+        <v>030217141005</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>individual</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D20"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/eauto-insurance/input-vehicles.xlsx
+++ b/scripts/eauto-insurance/input-vehicles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>JVK1779</v>
+        <v>VPM7358</v>
       </c>
       <c r="B2" t="str">
         <v>030217141005</v>
@@ -424,264 +424,12 @@
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>PRR5421</v>
-      </c>
-      <c r="B3" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>WB7932R</v>
-      </c>
-      <c r="B4" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>WTX9642</v>
-      </c>
-      <c r="B5" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>WEN7866</v>
-      </c>
-      <c r="B6" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>MCH2151</v>
-      </c>
-      <c r="B7" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>WTX9642</v>
-      </c>
-      <c r="B8" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>VMM949</v>
-      </c>
-      <c r="B9" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>JSS9468</v>
-      </c>
-      <c r="B10" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>RW3512</v>
-      </c>
-      <c r="B11" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>BKN9186</v>
-      </c>
-      <c r="B12" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>JLY4743</v>
-      </c>
-      <c r="B13" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>VBY8385</v>
-      </c>
-      <c r="B14" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>JPK5366</v>
-      </c>
-      <c r="B15" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>JGC7679</v>
-      </c>
-      <c r="B16" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>JLY4743</v>
-      </c>
-      <c r="B17" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>VPF1134</v>
-      </c>
-      <c r="B18" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>VCK772</v>
-      </c>
-      <c r="B19" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v>individual</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>VDS5747</v>
-      </c>
-      <c r="B20" t="str">
-        <v>030217141005</v>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
         <v>individual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>